--- a/202260812_CSAI_2026_Corporations_Data_Sheet_1_0467_1_filled.xlsx
+++ b/202260812_CSAI_2026_Corporations_Data_Sheet_1_0467_1_filled.xlsx
@@ -4962,7 +4962,8 @@
 • Openwave (Baku, 29–31 May 2026): final ranking from 4 jury members – 1. Digi Solution (330 pts), 2. ExaMinds (317), 3. Conflict (302), matching the winners reported in Tab 2.
 • Additional pitch event not listed in Tab 2: 23–24 Dec 2025, Azerbaijan State University of Economics (UNEC), “AİM (pitch)” – source lists 29 teams and 15 startups (Agrisense, Indefector, PlanneX, MailGuard, CentraSec AI, UBEx, Beacon, Smarthire, Payonaz, Valora, Autopay, TopHub, Tedrisync, SlicesMetric, AgroTrust AZ). Winners: 1st Enthuzone (4,000 AZN), 2nd Savai (2,500 AZN), 3rd ITeaguys (1,000 AZN). The corporate partner of this event is not stated in the source.
 • Commercial relationships (Tab 3): a review of the innovation.az startup catalogue (824 profiles, 22.09.2026) found no documented record naming a specific corporation as a startup's customer or supplier. 14 startups self-declare corporate target clients (e.g. banks, large enterprises), which is unverified, so no rows were added to Tab 3. The names of the 9 startups added to OBA's vendor list and the 2 OBA pilot projects are not available in the materials.
-• Baku Metro Hackathon: team names are not available in the supporting materials.</t>
+• Pitch decks: all 13 WaterTech decks and 14 of 15 Openwave decks were read (WaveNerve's deck is image-only; Digi Solution submitted a video). FinovateBank decks are hosted on Jotform and could not be opened, so those teams are listed from the submission sheet only.
+• Baku Metro Hackathon: the full team list is not in the materials. One Openwave deck (team Zəngəzur) lists 'Metro Hakaton 1-ci yer' (1st place) on its team slide – self-reported.</t>
         </is>
       </c>
     </row>
